--- a/5.26.26 Climate Tracker .xlsx
+++ b/5.26.26 Climate Tracker .xlsx
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I534"/>
+  <dimension ref="A1:I581"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -19757,6 +19757,1651 @@
         <v>0</v>
       </c>
       <c r="I534" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 581. 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 662</t>
+        </is>
+      </c>
+      <c r="B535" s="48" t="inlineStr">
+        <is>
+          <t>Promoting Domestic Energy Production Act</t>
+        </is>
+      </c>
+      <c r="C535" s="48" t="inlineStr"/>
+      <c r="D535" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Carey, Mike [R-OH-15] (R-OH-15)</t>
+        </is>
+      </c>
+      <c r="E535" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F535" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G535" s="48" t="n">
+        <v>17</v>
+      </c>
+      <c r="H535" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I535" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2025-01-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8517</t>
+        </is>
+      </c>
+      <c r="B536" s="48" t="inlineStr">
+        <is>
+          <t>Clean Energy Workforce Act</t>
+        </is>
+      </c>
+      <c r="C536" s="48" t="inlineStr"/>
+      <c r="D536" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Magaziner, Seth [D-RI-2] (D-RI-2)</t>
+        </is>
+      </c>
+      <c r="E536" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F536" s="48" t="n">
+        <v>19</v>
+      </c>
+      <c r="G536" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H536" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I536" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Education and Workforce. 2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8519</t>
+        </is>
+      </c>
+      <c r="B537" s="48" t="inlineStr">
+        <is>
+          <t>To require the Administrator of the Environmental Protection Agency to waive Reid Vapor Pressure requirements with respect to calendar year 2026, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C537" s="48" t="inlineStr"/>
+      <c r="D537" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Mast, Brian J. [R-FL-21] (R-FL-21)</t>
+        </is>
+      </c>
+      <c r="E537" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F537" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H537" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 3291</t>
+        </is>
+      </c>
+      <c r="B538" s="48" t="inlineStr">
+        <is>
+          <t>Certainty for Our Energy Future Act</t>
+        </is>
+      </c>
+      <c r="C538" s="48" t="inlineStr"/>
+      <c r="D538" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Kiggans, Jennifer A. [R-VA-2] (R-VA-2)</t>
+        </is>
+      </c>
+      <c r="E538" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F538" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G538" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="H538" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I538" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2025-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 2072</t>
+        </is>
+      </c>
+      <c r="B539" s="48" t="inlineStr">
+        <is>
+          <t>To require the Federal Energy Regulatory Commission to extend the time period during which licensees are required to commence construction of certain hydropower projects.</t>
+        </is>
+      </c>
+      <c r="C539" s="48" t="inlineStr"/>
+      <c r="D539" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Newhouse, Dan [R-WA-4] (R-WA-4)</t>
+        </is>
+      </c>
+      <c r="E539" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F539" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G539" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H539" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I539" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 408. 2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8496</t>
+        </is>
+      </c>
+      <c r="B540" s="48" t="inlineStr">
+        <is>
+          <t>Marine Mammal Climate Change Protection Act of 2026</t>
+        </is>
+      </c>
+      <c r="C540" s="48" t="inlineStr"/>
+      <c r="D540" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Brownley, Julia [D-CA-26] (D-CA-26)</t>
+        </is>
+      </c>
+      <c r="E540" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F540" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="G540" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H540" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I540" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8482</t>
+        </is>
+      </c>
+      <c r="B541" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Internal Revenue Code of 1986 to modify certain investment credit rules with respect to nuclear facilities.</t>
+        </is>
+      </c>
+      <c r="C541" s="48" t="inlineStr"/>
+      <c r="D541" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Harrigan, Pat [R-NC-10] (R-NC-10)</t>
+        </is>
+      </c>
+      <c r="E541" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="F541" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G541" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H541" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7977</t>
+        </is>
+      </c>
+      <c r="B542" s="48" t="inlineStr">
+        <is>
+          <t>Energy Bills Relief Act</t>
+        </is>
+      </c>
+      <c r="C542" s="48" t="inlineStr"/>
+      <c r="D542" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Casten, Sean [D-IL-6] (D-IL-6)</t>
+        </is>
+      </c>
+      <c r="E542" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F542" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G542" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H542" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I542" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Energy and Commerce, and in addition to the Committees on Agriculture, Ways and Means, Natural Resources, Financial Services, Transportation and Infrastructure, Education and Workforce, Oversight and Government Reform, and Science, Space, and Technology, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 317</t>
+        </is>
+      </c>
+      <c r="B543" s="48" t="inlineStr">
+        <is>
+          <t>Urging the United States to lead the world back from the brink of nuclear war and halt and reverse the nuclear arms race.</t>
+        </is>
+      </c>
+      <c r="C543" s="48" t="inlineStr"/>
+      <c r="D543" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. McGovern, James P. [D-MA-2] (D-MA-2)</t>
+        </is>
+      </c>
+      <c r="E543" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F543" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G543" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H543" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I543" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Foreign Affairs, and in addition to the Committee on Armed Services, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2025-04-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5692</t>
+        </is>
+      </c>
+      <c r="B544" s="48" t="inlineStr">
+        <is>
+          <t>Marine Energy Technologies Acceleration Act</t>
+        </is>
+      </c>
+      <c r="C544" s="48" t="inlineStr"/>
+      <c r="D544" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Barragán, Nanette Diaz [D-CA-44] (D-CA-44)</t>
+        </is>
+      </c>
+      <c r="E544" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F544" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G544" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H544" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I544" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Science, Space, and Technology, and in addition to the Committees on Energy and Commerce, Natural Resources, and Education and Workforce, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2025-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8497</t>
+        </is>
+      </c>
+      <c r="B545" s="48" t="inlineStr">
+        <is>
+          <t>Supporting Energy and Economic Development (SEED) Act</t>
+        </is>
+      </c>
+      <c r="C545" s="48" t="inlineStr"/>
+      <c r="D545" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Carey, Mike [R-OH-15] (R-OH-15)</t>
+        </is>
+      </c>
+      <c r="E545" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="F545" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G545" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="H545" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I545" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5823</t>
+        </is>
+      </c>
+      <c r="B546" s="48" t="inlineStr">
+        <is>
+          <t>Watershed Protection and Forest Recovery Act of 2025</t>
+        </is>
+      </c>
+      <c r="C546" s="48" t="inlineStr"/>
+      <c r="D546" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Neguse, Joe [D-CO-2] (D-CO-2)</t>
+        </is>
+      </c>
+      <c r="E546" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F546" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G546" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H546" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I546" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Agriculture. 2025-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 6204</t>
+        </is>
+      </c>
+      <c r="B547" s="48" t="inlineStr">
+        <is>
+          <t>Large-Scale Water Recycling Reauthorization Act</t>
+        </is>
+      </c>
+      <c r="C547" s="48" t="inlineStr"/>
+      <c r="D547" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Lee, Susie [D-NV-3] (D-NV-3)</t>
+        </is>
+      </c>
+      <c r="E547" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F547" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G547" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H547" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I547" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2025-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7960</t>
+        </is>
+      </c>
+      <c r="B548" s="48" t="inlineStr">
+        <is>
+          <t>Big Oil Windfall Profits Tax Act</t>
+        </is>
+      </c>
+      <c r="C548" s="48" t="inlineStr"/>
+      <c r="D548" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Khanna, Ro [D-CA-17] (D-CA-17)</t>
+        </is>
+      </c>
+      <c r="E548" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F548" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="G548" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H548" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I548" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1302</t>
+        </is>
+      </c>
+      <c r="B549" s="48" t="inlineStr">
+        <is>
+          <t>Designating May 2026 as "National Electrical Safety Month" in the United States and supporting the goals and ideals of "National Electrical Safety Month" to raise awareness of electrical hazards in homes, schools, and workplaces and the action citizens can take to protect against electrically related hazards.</t>
+        </is>
+      </c>
+      <c r="C549" s="48" t="inlineStr"/>
+      <c r="D549" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Bresnahan, Robert P. [R-PA-8] (R-PA-8)</t>
+        </is>
+      </c>
+      <c r="E549" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F549" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G549" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H549" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8889</t>
+        </is>
+      </c>
+      <c r="B550" s="48" t="inlineStr">
+        <is>
+          <t>To improve dam and hydropower safety, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C550" s="48" t="inlineStr"/>
+      <c r="D550" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Dingell, Debbie [D-MI-6] (D-MI-6)</t>
+        </is>
+      </c>
+      <c r="E550" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F550" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G550" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H550" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I550" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 972</t>
+        </is>
+      </c>
+      <c r="B551" s="48" t="inlineStr">
+        <is>
+          <t>Sloan Canyon Conservation and Lateral Pipeline Act</t>
+        </is>
+      </c>
+      <c r="C551" s="48" t="inlineStr"/>
+      <c r="D551" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Titus, Dina [D-NV-1] (D-NV-1)</t>
+        </is>
+      </c>
+      <c r="E551" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F551" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H551" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I551" s="48" t="inlineStr">
+        <is>
+          <t>Became Public Law No: 119-91. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8397</t>
+        </is>
+      </c>
+      <c r="B552" s="48" t="inlineStr">
+        <is>
+          <t>Protecting Moms and Babies Against Climate Change Act</t>
+        </is>
+      </c>
+      <c r="C552" s="48" t="inlineStr"/>
+      <c r="D552" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Underwood, Lauren [D-IL-14] (D-IL-14)</t>
+        </is>
+      </c>
+      <c r="E552" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F552" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G552" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I552" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8790</t>
+        </is>
+      </c>
+      <c r="B553" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Energy Independence and Security Act of 2007 to direct research, development, demonstration, and commercial application activities in support of next-generation geothermal and closed-loop geothermal systems in various conditions, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C553" s="48" t="inlineStr"/>
+      <c r="D553" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Harrigan, Pat [R-NC-10] (R-NC-10)</t>
+        </is>
+      </c>
+      <c r="E553" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F553" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G553" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H553" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I553" s="48" t="inlineStr">
+        <is>
+          <t>Ordered to be Reported (Amended) by Voice Vote. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 3564</t>
+        </is>
+      </c>
+      <c r="B554" s="48" t="inlineStr">
+        <is>
+          <t>The Nuclear First-Strike Security Act of 2025</t>
+        </is>
+      </c>
+      <c r="C554" s="48" t="inlineStr"/>
+      <c r="D554" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Peters, Scott H. [D-CA-50] (D-CA-50)</t>
+        </is>
+      </c>
+      <c r="E554" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F554" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G554" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H554" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I554" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Foreign Affairs, and in addition to the Committee on Armed Services, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2025-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8254</t>
+        </is>
+      </c>
+      <c r="B555" s="48" t="inlineStr">
+        <is>
+          <t>Water Access and Affordability Act</t>
+        </is>
+      </c>
+      <c r="C555" s="48" t="inlineStr"/>
+      <c r="D555" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Tlaib, Rashida [D-MI-12] (D-MI-12)</t>
+        </is>
+      </c>
+      <c r="E555" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="F555" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="G555" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H555" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I555" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Transportation and Infrastructure, and in addition to the Committees on Energy and Commerce, Oversight and Government Reform, and Ways and Means, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2026-04-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8027</t>
+        </is>
+      </c>
+      <c r="B556" s="48" t="inlineStr">
+        <is>
+          <t>Advanced Wastewater Treatment Assistance Act of 2026</t>
+        </is>
+      </c>
+      <c r="C556" s="48" t="inlineStr"/>
+      <c r="D556" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Stevens, Haley M. [D-MI-11] (D-MI-11)</t>
+        </is>
+      </c>
+      <c r="E556" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F556" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G556" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H556" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I556" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Transportation and Infrastructure. 2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1188</t>
+        </is>
+      </c>
+      <c r="B557" s="48" t="inlineStr">
+        <is>
+          <t>Expressing support for the work of open water lifeguards as first responders and emergency response providers.</t>
+        </is>
+      </c>
+      <c r="C557" s="48" t="inlineStr"/>
+      <c r="D557" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Smith, Christopher H. [R-NJ-4] (R-NJ-4)</t>
+        </is>
+      </c>
+      <c r="E557" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F557" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G557" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H557" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I557" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Transportation and Infrastructure. 2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 4733</t>
+        </is>
+      </c>
+      <c r="B558" s="48" t="inlineStr">
+        <is>
+          <t>Low-Income Household Water Assistance Program Establishment Act</t>
+        </is>
+      </c>
+      <c r="C558" s="48" t="inlineStr"/>
+      <c r="D558" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Sorensen, Eric [D-IL-17] (D-IL-17)</t>
+        </is>
+      </c>
+      <c r="E558" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F558" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="G558" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="H558" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I558" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Subcommittee on Water Resources and Environment. 2025-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8137</t>
+        </is>
+      </c>
+      <c r="B559" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Internal Revenue Code of 1986 to establish tax credits for the production of, and investment in, certain renewable materials.</t>
+        </is>
+      </c>
+      <c r="C559" s="48" t="inlineStr"/>
+      <c r="D559" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Fischbach, Michelle [R-MN-7] (R-MN-7)</t>
+        </is>
+      </c>
+      <c r="E559" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F559" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G559" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="H559" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 3978</t>
+        </is>
+      </c>
+      <c r="B560" s="48" t="inlineStr">
+        <is>
+          <t>Nuclear REFUEL (Recycling Efficient Fuels Utilizing Expedited Licensing) Act</t>
+        </is>
+      </c>
+      <c r="C560" s="48" t="inlineStr"/>
+      <c r="D560" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Latta, Robert E. [R-OH-5] (R-OH-5)</t>
+        </is>
+      </c>
+      <c r="E560" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F560" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="G560" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="H560" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2025-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 2109</t>
+        </is>
+      </c>
+      <c r="B561" s="48" t="inlineStr">
+        <is>
+          <t>Cybersecurity for Rural Water Systems Act</t>
+        </is>
+      </c>
+      <c r="C561" s="48" t="inlineStr"/>
+      <c r="D561" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Davis, Donald G. [D-NC-1] (D-NC-1)</t>
+        </is>
+      </c>
+      <c r="E561" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F561" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G561" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H561" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I561" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Subcommittee on Commodity Markets, Digital Assets, and Rural Development. 2025-04-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7129</t>
+        </is>
+      </c>
+      <c r="B562" s="48" t="inlineStr">
+        <is>
+          <t>Water Power Research and Development Reauthorization Act</t>
+        </is>
+      </c>
+      <c r="C562" s="48" t="inlineStr"/>
+      <c r="D562" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Bonamici, Suzanne [D-OR-1] (D-OR-1)</t>
+        </is>
+      </c>
+      <c r="E562" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F562" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G562" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H562" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I562" s="48" t="inlineStr">
+        <is>
+          <t>Ordered to be Reported (Amended) by Voice Vote. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8947</t>
+        </is>
+      </c>
+      <c r="B563" s="48" t="inlineStr">
+        <is>
+          <t>To require the Federal Energy Regulatory Commission to establish and maintain the National Utility Rate Change Tracker, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C563" s="48" t="inlineStr"/>
+      <c r="D563" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Vindman, Eugene Simon [D-VA-7] (D-VA-7)</t>
+        </is>
+      </c>
+      <c r="E563" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F563" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G563" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H563" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I563" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8948</t>
+        </is>
+      </c>
+      <c r="B564" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Public Utility Regulatory Policies Act of 1978 to require States to consider measures that limit the amount of retail utility rate increases an electric utility can request to once every 365 days.</t>
+        </is>
+      </c>
+      <c r="C564" s="48" t="inlineStr"/>
+      <c r="D564" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Vindman, Eugene Simon [D-VA-7] (D-VA-7)</t>
+        </is>
+      </c>
+      <c r="E564" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F564" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G564" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H564" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I564" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8924</t>
+        </is>
+      </c>
+      <c r="B565" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Wild and Scenic Rivers Act to designate the Mullica River watershed in New Jersey for study for potential designation as a wild and scenic river, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C565" s="48" t="inlineStr"/>
+      <c r="D565" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Conaway, Herbert C. [D-NJ-3] (D-NJ-3)</t>
+        </is>
+      </c>
+      <c r="E565" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F565" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G565" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H565" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I565" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8706</t>
+        </is>
+      </c>
+      <c r="B566" s="48" t="inlineStr">
+        <is>
+          <t>Better Energy Storage and Safety Act</t>
+        </is>
+      </c>
+      <c r="C566" s="48" t="inlineStr"/>
+      <c r="D566" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Panetta, Jimmy [D-CA-19] (D-CA-19)</t>
+        </is>
+      </c>
+      <c r="E566" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F566" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G566" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H566" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Science, Space, and Technology. 2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8935</t>
+        </is>
+      </c>
+      <c r="B567" s="48" t="inlineStr">
+        <is>
+          <t>Department of Energy Drone Defense Act</t>
+        </is>
+      </c>
+      <c r="C567" s="48" t="inlineStr"/>
+      <c r="D567" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Lee, Susie [D-NV-3] (D-NV-3)</t>
+        </is>
+      </c>
+      <c r="E567" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F567" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G567" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H567" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I567" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Oversight and Government Reform. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 398</t>
+        </is>
+      </c>
+      <c r="B568" s="48" t="inlineStr">
+        <is>
+          <t>Geothermal Cost-Recovery Authority Act of 2025</t>
+        </is>
+      </c>
+      <c r="C568" s="48" t="inlineStr"/>
+      <c r="D568" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Ocasio-Cortez, Alexandria [D-NY-14] (D-NY-14)</t>
+        </is>
+      </c>
+      <c r="E568" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F568" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G568" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H568" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I568" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 569. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5631</t>
+        </is>
+      </c>
+      <c r="B569" s="48" t="inlineStr">
+        <is>
+          <t>Geothermal Ombudsman for National Deployment and Optimal Reviews Act</t>
+        </is>
+      </c>
+      <c r="C569" s="48" t="inlineStr"/>
+      <c r="D569" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Hurd, Jeff [R-CO-3] (R-CO-3)</t>
+        </is>
+      </c>
+      <c r="E569" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F569" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G569" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H569" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I569" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 574. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5638</t>
+        </is>
+      </c>
+      <c r="B570" s="48" t="inlineStr">
+        <is>
+          <t>Geothermal Royalty Reform Act</t>
+        </is>
+      </c>
+      <c r="C570" s="48" t="inlineStr"/>
+      <c r="D570" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Kennedy, Mike [R-UT-3] (R-UT-3)</t>
+        </is>
+      </c>
+      <c r="E570" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F570" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G570" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H570" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I570" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 575. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5617</t>
+        </is>
+      </c>
+      <c r="B571" s="48" t="inlineStr">
+        <is>
+          <t>Geothermal Gold Book Development Act</t>
+        </is>
+      </c>
+      <c r="C571" s="48" t="inlineStr"/>
+      <c r="D571" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Ansari, Yassamin [D-AZ-3] (D-AZ-3)</t>
+        </is>
+      </c>
+      <c r="E571" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F571" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G571" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H571" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I571" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 573. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8850</t>
+        </is>
+      </c>
+      <c r="B572" s="48" t="inlineStr">
+        <is>
+          <t>To create dedicated funds to conserve butterflies in North America, plants in the Pacific Islands, freshwater mussels in the United States, and desert fish in the Southwest United States, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C572" s="48" t="inlineStr"/>
+      <c r="D572" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Grijalva, Adelita S. [D-AZ-7] (D-AZ-7)</t>
+        </is>
+      </c>
+      <c r="E572" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F572" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="G572" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H572" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I572" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7450</t>
+        </is>
+      </c>
+      <c r="B573" s="48" t="inlineStr">
+        <is>
+          <t>Disaster Zone Energy Affordability and Investment Act</t>
+        </is>
+      </c>
+      <c r="C573" s="48" t="inlineStr"/>
+      <c r="D573" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Steube, W. Gregory [R-FL-17] (R-FL-17)</t>
+        </is>
+      </c>
+      <c r="E573" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F573" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G573" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="H573" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I573" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7069</t>
+        </is>
+      </c>
+      <c r="B574" s="48" t="inlineStr">
+        <is>
+          <t>Affordable Food and Energy Act of 2026</t>
+        </is>
+      </c>
+      <c r="C574" s="48" t="inlineStr"/>
+      <c r="D574" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. McDonald Rivet, Kristen [D-MI-8] (D-MI-8)</t>
+        </is>
+      </c>
+      <c r="E574" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F574" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G574" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H574" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I574" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Subcommittee on Nutrition and Foreign Agriculture. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1318</t>
+        </is>
+      </c>
+      <c r="B575" s="48" t="inlineStr">
+        <is>
+          <t>Expressing support for the designation of the month of May 2026 as "Progressive Supranuclear Palsy and Corticobasal Degeneration Awareness Month".</t>
+        </is>
+      </c>
+      <c r="C575" s="48" t="inlineStr"/>
+      <c r="D575" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Subramanyam, Suhas [D-VA-10] (D-VA-10)</t>
+        </is>
+      </c>
+      <c r="E575" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F575" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="G575" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H575" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I575" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1315</t>
+        </is>
+      </c>
+      <c r="B576" s="48" t="inlineStr">
+        <is>
+          <t>Expressing support for the designation of May 2026 as "Renewable Fuels Month" to recognize the important role that renewable fuels play in lowering fuel prices for consumers, lessening reliance on foreign adversaries, supporting rural communities, and reducing carbon impacts.</t>
+        </is>
+      </c>
+      <c r="C576" s="48" t="inlineStr"/>
+      <c r="D576" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Nunn, Zachary [R-IA-3] (R-IA-3)</t>
+        </is>
+      </c>
+      <c r="E576" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F576" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G576" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H576" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I576" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8998</t>
+        </is>
+      </c>
+      <c r="B577" s="48" t="inlineStr">
+        <is>
+          <t>To require the Transportation Research Board to evaluate innovative hull designs and the use of alternative material construction technologies to enhance operational fleet performance and payload capacity of waterborne transit systems.</t>
+        </is>
+      </c>
+      <c r="C577" s="48" t="inlineStr"/>
+      <c r="D577" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Scholten, Hillary J. [D-MI-3] (D-MI-3)</t>
+        </is>
+      </c>
+      <c r="E577" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F577" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H577" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I577" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Transportation and Infrastructure. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8990</t>
+        </is>
+      </c>
+      <c r="B578" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Clean Air Act to exclude marginal wells from certain standards of performance and other requirements under such Act, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C578" s="48" t="inlineStr"/>
+      <c r="D578" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Pfluger, August [R-TX-11] (R-TX-11)</t>
+        </is>
+      </c>
+      <c r="E578" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="F578" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G578" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="H578" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I578" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8969</t>
+        </is>
+      </c>
+      <c r="B579" s="48" t="inlineStr">
+        <is>
+          <t>To realign the nuclear forensics and attribution activities of the Federal Government from the Department of Homeland Security to the National Nuclear Security Administration.</t>
+        </is>
+      </c>
+      <c r="C579" s="48" t="inlineStr"/>
+      <c r="D579" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Foster, Bill [D-IL-11] (D-IL-11)</t>
+        </is>
+      </c>
+      <c r="E579" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F579" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G579" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H579" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I579" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Energy and Commerce, and in addition to the Committees on Homeland Security, Armed Services, and Foreign Affairs, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 9019</t>
+        </is>
+      </c>
+      <c r="B580" s="48" t="inlineStr">
+        <is>
+          <t>To direct the Secretary of Energy to report to Congress on the use of electric energy and water by certain data centers, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C580" s="48" t="inlineStr"/>
+      <c r="D580" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Roy, Chip [R-TX-21] (R-TX-21)</t>
+        </is>
+      </c>
+      <c r="E580" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F580" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G580" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H580" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I580" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 9022</t>
+        </is>
+      </c>
+      <c r="B581" s="48" t="inlineStr">
+        <is>
+          <t>Energy and Water Development and Related Agencies Appropriations Act, 2027</t>
+        </is>
+      </c>
+      <c r="C581" s="48" t="inlineStr"/>
+      <c r="D581" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Fleischmann, Charles J. "Chuck" [R-TN-3] (R-TN-3)</t>
+        </is>
+      </c>
+      <c r="E581" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F581" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G581" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H581" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I581" s="48" t="inlineStr">
         <is>
           <t>Placed on the Union Calendar, Calendar No. 581. 2026-05-22</t>
         </is>
@@ -20221,7 +21866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I264"/>
+  <dimension ref="A1:I284"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="24" min="1" max="1"/>
@@ -29864,17 +31509,706 @@
         </is>
       </c>
     </row>
-    <row r="265" ht="60" customHeight="1"/>
-    <row r="266" ht="60" customHeight="1"/>
-    <row r="267" ht="60" customHeight="1"/>
-    <row r="268" ht="60" customHeight="1"/>
-    <row r="269" ht="60" customHeight="1"/>
-    <row r="270" ht="60" customHeight="1"/>
-    <row r="271" ht="60" customHeight="1"/>
-    <row r="272" ht="60" customHeight="1"/>
-    <row r="273" ht="60" customHeight="1"/>
-    <row r="274" ht="60" customHeight="1"/>
-    <row r="275" ht="60" customHeight="1"/>
+    <row r="265" ht="60" customHeight="1">
+      <c r="A265" s="48" t="inlineStr">
+        <is>
+          <t>S. 4351</t>
+        </is>
+      </c>
+      <c r="B265" s="48" t="inlineStr">
+        <is>
+          <t>Energy Consumer Protection Act of 2026</t>
+        </is>
+      </c>
+      <c r="C265" s="48" t="inlineStr"/>
+      <c r="D265" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Cortez Masto, Catherine [D-NV] (D-NV)</t>
+        </is>
+      </c>
+      <c r="E265" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G265" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="60" customHeight="1">
+      <c r="A266" s="48" t="inlineStr">
+        <is>
+          <t>S. 1020</t>
+        </is>
+      </c>
+      <c r="B266" s="48" t="inlineStr">
+        <is>
+          <t>A bill to require the Federal Energy Regulatory Commission to extend the time period during which licensees are required to commence construction of certain hydropower projects.</t>
+        </is>
+      </c>
+      <c r="C266" s="48" t="inlineStr"/>
+      <c r="D266" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Daines, Steve [R-MT] (R-MT)</t>
+        </is>
+      </c>
+      <c r="E266" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="F266" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G266" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H266" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" s="48" t="inlineStr">
+        <is>
+          <t>Became Public Law No: 119-90. 2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="60" customHeight="1">
+      <c r="A267" s="48" t="inlineStr">
+        <is>
+          <t>S. 4475</t>
+        </is>
+      </c>
+      <c r="B267" s="48" t="inlineStr">
+        <is>
+          <t>Unlock American Energy and Jobs Act of 2026</t>
+        </is>
+      </c>
+      <c r="C267" s="48" t="inlineStr"/>
+      <c r="D267" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. McCormick, David [R-PA] (R-PA)</t>
+        </is>
+      </c>
+      <c r="E267" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="60" customHeight="1">
+      <c r="A268" s="48" t="inlineStr">
+        <is>
+          <t>S. 4506</t>
+        </is>
+      </c>
+      <c r="B268" s="48" t="inlineStr">
+        <is>
+          <t>Advancing Water Reuse Act</t>
+        </is>
+      </c>
+      <c r="C268" s="48" t="inlineStr"/>
+      <c r="D268" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Luján, Ben Ray [D-NM] (D-NM)</t>
+        </is>
+      </c>
+      <c r="E268" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F268" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Finance. 2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="60" customHeight="1">
+      <c r="A269" s="48" t="inlineStr">
+        <is>
+          <t>S. 4559</t>
+        </is>
+      </c>
+      <c r="B269" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Federal Power Act to require the Federal Energy Regulatory Commission to issue a final rule relating to the interconnection of large load facilities with the transmission system, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C269" s="48" t="inlineStr"/>
+      <c r="D269" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Schiff, Adam B. [D-CA] (D-CA)</t>
+        </is>
+      </c>
+      <c r="E269" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="60" customHeight="1">
+      <c r="A270" s="48" t="inlineStr">
+        <is>
+          <t>S. 857</t>
+        </is>
+      </c>
+      <c r="B270" s="48" t="inlineStr">
+        <is>
+          <t>Water Conservation Rebate Tax Parity Act</t>
+        </is>
+      </c>
+      <c r="C270" s="48" t="inlineStr"/>
+      <c r="D270" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Curtis, John R. [R-UT] (R-UT)</t>
+        </is>
+      </c>
+      <c r="E270" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F270" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="G270" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Finance. 2025-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="60" customHeight="1">
+      <c r="A271" s="48" t="inlineStr">
+        <is>
+          <t>S. 4536</t>
+        </is>
+      </c>
+      <c r="B271" s="48" t="inlineStr">
+        <is>
+          <t>Protecting America's Drinking Water from Extreme Temperatures Act of 2026</t>
+        </is>
+      </c>
+      <c r="C271" s="48" t="inlineStr"/>
+      <c r="D271" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Rosen, Jacky [D-NV] (D-NV)</t>
+        </is>
+      </c>
+      <c r="E271" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F271" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G271" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H271" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="60" customHeight="1">
+      <c r="A272" s="48" t="inlineStr">
+        <is>
+          <t>S. 4571</t>
+        </is>
+      </c>
+      <c r="B272" s="48" t="inlineStr">
+        <is>
+          <t>A bill to require the Environmental Protection Agency to establish a tropospheric ozone research program, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C272" s="48" t="inlineStr"/>
+      <c r="D272" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Whitehouse, Sheldon [D-RI] (D-RI)</t>
+        </is>
+      </c>
+      <c r="E272" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F272" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G272" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="60" customHeight="1">
+      <c r="A273" s="48" t="inlineStr">
+        <is>
+          <t>S.J.RES. 188</t>
+        </is>
+      </c>
+      <c r="B273" s="48" t="inlineStr">
+        <is>
+          <t>A joint resolution providing for congressional disapproval under chapter 8 of title 5, United States Code, of the rule submitted by the Environmental Protection Agency relating to "National Emission Standards for Hazardous Air Pollutants: Coal- and Oil-Fired Electric Utility Steam Generating Units: Final Repeal".</t>
+        </is>
+      </c>
+      <c r="C273" s="48" t="inlineStr"/>
+      <c r="D273" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Whitehouse, Sheldon [D-RI] (D-RI)</t>
+        </is>
+      </c>
+      <c r="E273" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" s="48" t="inlineStr">
+        <is>
+          <t>Placed on Senate Legislative Calendar under General Orders. Calendar No. 409. 2026-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="60" customHeight="1">
+      <c r="A274" s="48" t="inlineStr">
+        <is>
+          <t>S. 4406</t>
+        </is>
+      </c>
+      <c r="B274" s="48" t="inlineStr">
+        <is>
+          <t>Next-Generation Geothermal Research and Development Act</t>
+        </is>
+      </c>
+      <c r="C274" s="48" t="inlineStr"/>
+      <c r="D274" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Cortez Masto, Catherine [D-NV] (D-NV)</t>
+        </is>
+      </c>
+      <c r="E274" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F274" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H274" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="60" customHeight="1">
+      <c r="A275" s="48" t="inlineStr">
+        <is>
+          <t>S. 4585</t>
+        </is>
+      </c>
+      <c r="B275" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Federal Reserve Act to mandate discount window testing, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C275" s="48" t="inlineStr"/>
+      <c r="D275" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Warner, Mark R. [D-VA] (D-VA)</t>
+        </is>
+      </c>
+      <c r="E275" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F275" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Banking, Housing, and Urban Affairs. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="48" t="inlineStr">
+        <is>
+          <t>S. 4595</t>
+        </is>
+      </c>
+      <c r="B276" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Wild and Scenic Rivers Act to designate the Mullica River watershed in New Jersey for study for potential designation as a wild and scenic river, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C276" s="48" t="inlineStr"/>
+      <c r="D276" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Kim, Andy [D-NJ] (D-NJ)</t>
+        </is>
+      </c>
+      <c r="E276" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F276" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="48" t="inlineStr">
+        <is>
+          <t>S. 4610</t>
+        </is>
+      </c>
+      <c r="B277" s="48" t="inlineStr">
+        <is>
+          <t>A bill to promote the development and use of geothermal resources in the Pacific, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C277" s="48" t="inlineStr"/>
+      <c r="D277" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Schatz, Brian [D-HI] (D-HI)</t>
+        </is>
+      </c>
+      <c r="E277" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F277" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G277" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H277" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Foreign Relations. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="48" t="inlineStr">
+        <is>
+          <t>S. 4605</t>
+        </is>
+      </c>
+      <c r="B278" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Geothermal Steam Act of 1970 to provide cost-recovery authority for the Department of the Interior.</t>
+        </is>
+      </c>
+      <c r="C278" s="48" t="inlineStr"/>
+      <c r="D278" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Gallego, Ruben [D-AZ] (D-AZ)</t>
+        </is>
+      </c>
+      <c r="E278" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H278" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="48" t="inlineStr">
+        <is>
+          <t>S. 4529</t>
+        </is>
+      </c>
+      <c r="B279" s="48" t="inlineStr">
+        <is>
+          <t>Build Nuclear with Local Materials Act of 2026</t>
+        </is>
+      </c>
+      <c r="C279" s="48" t="inlineStr"/>
+      <c r="D279" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Lummis, Cynthia M. [R-WY] (R-WY)</t>
+        </is>
+      </c>
+      <c r="E279" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F279" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G279" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" s="48" t="inlineStr">
+        <is>
+          <t>Committee on Environment and Public Works Subcommittee on Clean Air, Climate, and Nuclear Innovation and Safety. Hearings held. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="48" t="inlineStr">
+        <is>
+          <t>S. 510</t>
+        </is>
+      </c>
+      <c r="B280" s="48" t="inlineStr">
+        <is>
+          <t>Financing Our Energy Future Act</t>
+        </is>
+      </c>
+      <c r="C280" s="48" t="inlineStr"/>
+      <c r="D280" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Moran, Jerry [R-KS] (R-KS)</t>
+        </is>
+      </c>
+      <c r="E280" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F280" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G280" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="H280" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I280" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Finance. 2025-02-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="48" t="inlineStr">
+        <is>
+          <t>S. 4549</t>
+        </is>
+      </c>
+      <c r="B281" s="48" t="inlineStr">
+        <is>
+          <t>WATER for Farmers Act</t>
+        </is>
+      </c>
+      <c r="C281" s="48" t="inlineStr"/>
+      <c r="D281" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Cornyn, John [R-TX] (R-TX)</t>
+        </is>
+      </c>
+      <c r="E281" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Foreign Relations. 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="48" t="inlineStr">
+        <is>
+          <t>S. 4619</t>
+        </is>
+      </c>
+      <c r="B282" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Clean Air Act to exclude marginal wells from certain standards of performance and other requirements under that Act, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C282" s="48" t="inlineStr"/>
+      <c r="D282" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Lummis, Cynthia M. [R-WY] (R-WY)</t>
+        </is>
+      </c>
+      <c r="E282" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F282" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H282" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="48" t="inlineStr">
+        <is>
+          <t>S.RES. 752</t>
+        </is>
+      </c>
+      <c r="B283" s="48" t="inlineStr">
+        <is>
+          <t>A resolution expressing support for the designation of the month of May 2026 as "Progressive Supranuclear Palsy and Corticobasal Degeneration Awareness Month".</t>
+        </is>
+      </c>
+      <c r="C283" s="48" t="inlineStr"/>
+      <c r="D283" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Blumenthal, Richard [D-CT] (D-CT)</t>
+        </is>
+      </c>
+      <c r="E283" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Health, Education, Labor, and Pensions. (text: CR S2447) 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="48" t="inlineStr">
+        <is>
+          <t>S.RES. 747</t>
+        </is>
+      </c>
+      <c r="B284" s="48" t="inlineStr">
+        <is>
+          <t>A resolution expressing support for the designation of May 2026 as "Renewable Fuels Month" to recognize the important role that renewable fuels play in lowering fuel prices for consumers, lessening reliance on foreign adversaries, supporting rural communities, and reducing carbon impacts.</t>
+        </is>
+      </c>
+      <c r="C284" s="48" t="inlineStr"/>
+      <c r="D284" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Ricketts, Pete [R-NE] (R-NE)</t>
+        </is>
+      </c>
+      <c r="E284" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F284" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G284" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H284" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" s="48" t="inlineStr">
+        <is>
+          <t>Submitted in the Senate, considered, and agreed to without amendment and with a preamble by Voice Vote. (consideration: CR S2435; text: CR S2445) 2026-05-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D4"/>

--- a/5.26.26 Climate Tracker .xlsx
+++ b/5.26.26 Climate Tracker .xlsx
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I581"/>
+  <dimension ref="A1:I628"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -21402,6 +21402,1651 @@
         <v>0</v>
       </c>
       <c r="I581" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 581. 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 662</t>
+        </is>
+      </c>
+      <c r="B582" s="48" t="inlineStr">
+        <is>
+          <t>Promoting Domestic Energy Production Act</t>
+        </is>
+      </c>
+      <c r="C582" s="48" t="inlineStr"/>
+      <c r="D582" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Carey, Mike [R-OH-15] (R-OH-15)</t>
+        </is>
+      </c>
+      <c r="E582" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F582" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G582" s="48" t="n">
+        <v>17</v>
+      </c>
+      <c r="H582" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I582" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2025-01-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8517</t>
+        </is>
+      </c>
+      <c r="B583" s="48" t="inlineStr">
+        <is>
+          <t>Clean Energy Workforce Act</t>
+        </is>
+      </c>
+      <c r="C583" s="48" t="inlineStr"/>
+      <c r="D583" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Magaziner, Seth [D-RI-2] (D-RI-2)</t>
+        </is>
+      </c>
+      <c r="E583" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F583" s="48" t="n">
+        <v>19</v>
+      </c>
+      <c r="G583" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H583" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I583" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Education and Workforce. 2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8519</t>
+        </is>
+      </c>
+      <c r="B584" s="48" t="inlineStr">
+        <is>
+          <t>To require the Administrator of the Environmental Protection Agency to waive Reid Vapor Pressure requirements with respect to calendar year 2026, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C584" s="48" t="inlineStr"/>
+      <c r="D584" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Mast, Brian J. [R-FL-21] (R-FL-21)</t>
+        </is>
+      </c>
+      <c r="E584" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F584" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G584" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H584" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I584" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 3291</t>
+        </is>
+      </c>
+      <c r="B585" s="48" t="inlineStr">
+        <is>
+          <t>Certainty for Our Energy Future Act</t>
+        </is>
+      </c>
+      <c r="C585" s="48" t="inlineStr"/>
+      <c r="D585" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Kiggans, Jennifer A. [R-VA-2] (R-VA-2)</t>
+        </is>
+      </c>
+      <c r="E585" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F585" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G585" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="H585" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I585" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2025-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 2072</t>
+        </is>
+      </c>
+      <c r="B586" s="48" t="inlineStr">
+        <is>
+          <t>To require the Federal Energy Regulatory Commission to extend the time period during which licensees are required to commence construction of certain hydropower projects.</t>
+        </is>
+      </c>
+      <c r="C586" s="48" t="inlineStr"/>
+      <c r="D586" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Newhouse, Dan [R-WA-4] (R-WA-4)</t>
+        </is>
+      </c>
+      <c r="E586" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F586" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G586" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H586" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I586" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 408. 2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8496</t>
+        </is>
+      </c>
+      <c r="B587" s="48" t="inlineStr">
+        <is>
+          <t>Marine Mammal Climate Change Protection Act of 2026</t>
+        </is>
+      </c>
+      <c r="C587" s="48" t="inlineStr"/>
+      <c r="D587" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Brownley, Julia [D-CA-26] (D-CA-26)</t>
+        </is>
+      </c>
+      <c r="E587" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F587" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="G587" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H587" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I587" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8482</t>
+        </is>
+      </c>
+      <c r="B588" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Internal Revenue Code of 1986 to modify certain investment credit rules with respect to nuclear facilities.</t>
+        </is>
+      </c>
+      <c r="C588" s="48" t="inlineStr"/>
+      <c r="D588" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Harrigan, Pat [R-NC-10] (R-NC-10)</t>
+        </is>
+      </c>
+      <c r="E588" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="F588" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G588" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H588" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I588" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7977</t>
+        </is>
+      </c>
+      <c r="B589" s="48" t="inlineStr">
+        <is>
+          <t>Energy Bills Relief Act</t>
+        </is>
+      </c>
+      <c r="C589" s="48" t="inlineStr"/>
+      <c r="D589" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Casten, Sean [D-IL-6] (D-IL-6)</t>
+        </is>
+      </c>
+      <c r="E589" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F589" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G589" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H589" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I589" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Energy and Commerce, and in addition to the Committees on Agriculture, Ways and Means, Natural Resources, Financial Services, Transportation and Infrastructure, Education and Workforce, Oversight and Government Reform, and Science, Space, and Technology, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 317</t>
+        </is>
+      </c>
+      <c r="B590" s="48" t="inlineStr">
+        <is>
+          <t>Urging the United States to lead the world back from the brink of nuclear war and halt and reverse the nuclear arms race.</t>
+        </is>
+      </c>
+      <c r="C590" s="48" t="inlineStr"/>
+      <c r="D590" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. McGovern, James P. [D-MA-2] (D-MA-2)</t>
+        </is>
+      </c>
+      <c r="E590" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F590" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G590" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H590" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I590" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Foreign Affairs, and in addition to the Committee on Armed Services, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2025-04-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5692</t>
+        </is>
+      </c>
+      <c r="B591" s="48" t="inlineStr">
+        <is>
+          <t>Marine Energy Technologies Acceleration Act</t>
+        </is>
+      </c>
+      <c r="C591" s="48" t="inlineStr"/>
+      <c r="D591" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Barragán, Nanette Diaz [D-CA-44] (D-CA-44)</t>
+        </is>
+      </c>
+      <c r="E591" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F591" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G591" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H591" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I591" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Science, Space, and Technology, and in addition to the Committees on Energy and Commerce, Natural Resources, and Education and Workforce, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2025-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8497</t>
+        </is>
+      </c>
+      <c r="B592" s="48" t="inlineStr">
+        <is>
+          <t>Supporting Energy and Economic Development (SEED) Act</t>
+        </is>
+      </c>
+      <c r="C592" s="48" t="inlineStr"/>
+      <c r="D592" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Carey, Mike [R-OH-15] (R-OH-15)</t>
+        </is>
+      </c>
+      <c r="E592" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="F592" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G592" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="H592" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I592" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5823</t>
+        </is>
+      </c>
+      <c r="B593" s="48" t="inlineStr">
+        <is>
+          <t>Watershed Protection and Forest Recovery Act of 2025</t>
+        </is>
+      </c>
+      <c r="C593" s="48" t="inlineStr"/>
+      <c r="D593" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Neguse, Joe [D-CO-2] (D-CO-2)</t>
+        </is>
+      </c>
+      <c r="E593" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F593" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G593" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H593" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I593" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Agriculture. 2025-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 6204</t>
+        </is>
+      </c>
+      <c r="B594" s="48" t="inlineStr">
+        <is>
+          <t>Large-Scale Water Recycling Reauthorization Act</t>
+        </is>
+      </c>
+      <c r="C594" s="48" t="inlineStr"/>
+      <c r="D594" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Lee, Susie [D-NV-3] (D-NV-3)</t>
+        </is>
+      </c>
+      <c r="E594" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F594" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G594" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H594" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I594" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2025-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7960</t>
+        </is>
+      </c>
+      <c r="B595" s="48" t="inlineStr">
+        <is>
+          <t>Big Oil Windfall Profits Tax Act</t>
+        </is>
+      </c>
+      <c r="C595" s="48" t="inlineStr"/>
+      <c r="D595" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Khanna, Ro [D-CA-17] (D-CA-17)</t>
+        </is>
+      </c>
+      <c r="E595" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F595" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="G595" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H595" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I595" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1302</t>
+        </is>
+      </c>
+      <c r="B596" s="48" t="inlineStr">
+        <is>
+          <t>Designating May 2026 as "National Electrical Safety Month" in the United States and supporting the goals and ideals of "National Electrical Safety Month" to raise awareness of electrical hazards in homes, schools, and workplaces and the action citizens can take to protect against electrically related hazards.</t>
+        </is>
+      </c>
+      <c r="C596" s="48" t="inlineStr"/>
+      <c r="D596" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Bresnahan, Robert P. [R-PA-8] (R-PA-8)</t>
+        </is>
+      </c>
+      <c r="E596" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F596" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G596" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H596" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I596" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8889</t>
+        </is>
+      </c>
+      <c r="B597" s="48" t="inlineStr">
+        <is>
+          <t>To improve dam and hydropower safety, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C597" s="48" t="inlineStr"/>
+      <c r="D597" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Dingell, Debbie [D-MI-6] (D-MI-6)</t>
+        </is>
+      </c>
+      <c r="E597" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F597" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G597" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H597" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I597" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 972</t>
+        </is>
+      </c>
+      <c r="B598" s="48" t="inlineStr">
+        <is>
+          <t>Sloan Canyon Conservation and Lateral Pipeline Act</t>
+        </is>
+      </c>
+      <c r="C598" s="48" t="inlineStr"/>
+      <c r="D598" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Titus, Dina [D-NV-1] (D-NV-1)</t>
+        </is>
+      </c>
+      <c r="E598" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F598" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G598" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H598" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I598" s="48" t="inlineStr">
+        <is>
+          <t>Became Public Law No: 119-91. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8397</t>
+        </is>
+      </c>
+      <c r="B599" s="48" t="inlineStr">
+        <is>
+          <t>Protecting Moms and Babies Against Climate Change Act</t>
+        </is>
+      </c>
+      <c r="C599" s="48" t="inlineStr"/>
+      <c r="D599" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Underwood, Lauren [D-IL-14] (D-IL-14)</t>
+        </is>
+      </c>
+      <c r="E599" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F599" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G599" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H599" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I599" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8790</t>
+        </is>
+      </c>
+      <c r="B600" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Energy Independence and Security Act of 2007 to direct research, development, demonstration, and commercial application activities in support of next-generation geothermal and closed-loop geothermal systems in various conditions, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C600" s="48" t="inlineStr"/>
+      <c r="D600" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Harrigan, Pat [R-NC-10] (R-NC-10)</t>
+        </is>
+      </c>
+      <c r="E600" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F600" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G600" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H600" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I600" s="48" t="inlineStr">
+        <is>
+          <t>Ordered to be Reported (Amended) by Voice Vote. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 3564</t>
+        </is>
+      </c>
+      <c r="B601" s="48" t="inlineStr">
+        <is>
+          <t>The Nuclear First-Strike Security Act of 2025</t>
+        </is>
+      </c>
+      <c r="C601" s="48" t="inlineStr"/>
+      <c r="D601" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Peters, Scott H. [D-CA-50] (D-CA-50)</t>
+        </is>
+      </c>
+      <c r="E601" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F601" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G601" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H601" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I601" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Foreign Affairs, and in addition to the Committee on Armed Services, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2025-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8254</t>
+        </is>
+      </c>
+      <c r="B602" s="48" t="inlineStr">
+        <is>
+          <t>Water Access and Affordability Act</t>
+        </is>
+      </c>
+      <c r="C602" s="48" t="inlineStr"/>
+      <c r="D602" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Tlaib, Rashida [D-MI-12] (D-MI-12)</t>
+        </is>
+      </c>
+      <c r="E602" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="F602" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="G602" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H602" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I602" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Transportation and Infrastructure, and in addition to the Committees on Energy and Commerce, Oversight and Government Reform, and Ways and Means, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2026-04-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8027</t>
+        </is>
+      </c>
+      <c r="B603" s="48" t="inlineStr">
+        <is>
+          <t>Advanced Wastewater Treatment Assistance Act of 2026</t>
+        </is>
+      </c>
+      <c r="C603" s="48" t="inlineStr"/>
+      <c r="D603" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Stevens, Haley M. [D-MI-11] (D-MI-11)</t>
+        </is>
+      </c>
+      <c r="E603" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F603" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G603" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H603" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I603" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Transportation and Infrastructure. 2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1188</t>
+        </is>
+      </c>
+      <c r="B604" s="48" t="inlineStr">
+        <is>
+          <t>Expressing support for the work of open water lifeguards as first responders and emergency response providers.</t>
+        </is>
+      </c>
+      <c r="C604" s="48" t="inlineStr"/>
+      <c r="D604" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Smith, Christopher H. [R-NJ-4] (R-NJ-4)</t>
+        </is>
+      </c>
+      <c r="E604" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F604" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G604" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H604" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I604" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Transportation and Infrastructure. 2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 4733</t>
+        </is>
+      </c>
+      <c r="B605" s="48" t="inlineStr">
+        <is>
+          <t>Low-Income Household Water Assistance Program Establishment Act</t>
+        </is>
+      </c>
+      <c r="C605" s="48" t="inlineStr"/>
+      <c r="D605" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Sorensen, Eric [D-IL-17] (D-IL-17)</t>
+        </is>
+      </c>
+      <c r="E605" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F605" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="G605" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="H605" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I605" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Subcommittee on Water Resources and Environment. 2025-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8137</t>
+        </is>
+      </c>
+      <c r="B606" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Internal Revenue Code of 1986 to establish tax credits for the production of, and investment in, certain renewable materials.</t>
+        </is>
+      </c>
+      <c r="C606" s="48" t="inlineStr"/>
+      <c r="D606" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Fischbach, Michelle [R-MN-7] (R-MN-7)</t>
+        </is>
+      </c>
+      <c r="E606" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F606" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G606" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="H606" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 3978</t>
+        </is>
+      </c>
+      <c r="B607" s="48" t="inlineStr">
+        <is>
+          <t>Nuclear REFUEL (Recycling Efficient Fuels Utilizing Expedited Licensing) Act</t>
+        </is>
+      </c>
+      <c r="C607" s="48" t="inlineStr"/>
+      <c r="D607" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Latta, Robert E. [R-OH-5] (R-OH-5)</t>
+        </is>
+      </c>
+      <c r="E607" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F607" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="G607" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="H607" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I607" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2025-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 2109</t>
+        </is>
+      </c>
+      <c r="B608" s="48" t="inlineStr">
+        <is>
+          <t>Cybersecurity for Rural Water Systems Act</t>
+        </is>
+      </c>
+      <c r="C608" s="48" t="inlineStr"/>
+      <c r="D608" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Davis, Donald G. [D-NC-1] (D-NC-1)</t>
+        </is>
+      </c>
+      <c r="E608" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F608" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G608" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H608" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I608" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Subcommittee on Commodity Markets, Digital Assets, and Rural Development. 2025-04-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7129</t>
+        </is>
+      </c>
+      <c r="B609" s="48" t="inlineStr">
+        <is>
+          <t>Water Power Research and Development Reauthorization Act</t>
+        </is>
+      </c>
+      <c r="C609" s="48" t="inlineStr"/>
+      <c r="D609" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Bonamici, Suzanne [D-OR-1] (D-OR-1)</t>
+        </is>
+      </c>
+      <c r="E609" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F609" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G609" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H609" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I609" s="48" t="inlineStr">
+        <is>
+          <t>Ordered to be Reported (Amended) by Voice Vote. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8947</t>
+        </is>
+      </c>
+      <c r="B610" s="48" t="inlineStr">
+        <is>
+          <t>To require the Federal Energy Regulatory Commission to establish and maintain the National Utility Rate Change Tracker, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C610" s="48" t="inlineStr"/>
+      <c r="D610" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Vindman, Eugene Simon [D-VA-7] (D-VA-7)</t>
+        </is>
+      </c>
+      <c r="E610" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F610" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G610" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H610" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I610" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8948</t>
+        </is>
+      </c>
+      <c r="B611" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Public Utility Regulatory Policies Act of 1978 to require States to consider measures that limit the amount of retail utility rate increases an electric utility can request to once every 365 days.</t>
+        </is>
+      </c>
+      <c r="C611" s="48" t="inlineStr"/>
+      <c r="D611" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Vindman, Eugene Simon [D-VA-7] (D-VA-7)</t>
+        </is>
+      </c>
+      <c r="E611" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F611" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G611" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H611" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I611" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8924</t>
+        </is>
+      </c>
+      <c r="B612" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Wild and Scenic Rivers Act to designate the Mullica River watershed in New Jersey for study for potential designation as a wild and scenic river, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C612" s="48" t="inlineStr"/>
+      <c r="D612" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Conaway, Herbert C. [D-NJ-3] (D-NJ-3)</t>
+        </is>
+      </c>
+      <c r="E612" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F612" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G612" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H612" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I612" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8706</t>
+        </is>
+      </c>
+      <c r="B613" s="48" t="inlineStr">
+        <is>
+          <t>Better Energy Storage and Safety Act</t>
+        </is>
+      </c>
+      <c r="C613" s="48" t="inlineStr"/>
+      <c r="D613" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Panetta, Jimmy [D-CA-19] (D-CA-19)</t>
+        </is>
+      </c>
+      <c r="E613" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F613" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G613" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H613" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I613" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Science, Space, and Technology. 2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8935</t>
+        </is>
+      </c>
+      <c r="B614" s="48" t="inlineStr">
+        <is>
+          <t>Department of Energy Drone Defense Act</t>
+        </is>
+      </c>
+      <c r="C614" s="48" t="inlineStr"/>
+      <c r="D614" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Lee, Susie [D-NV-3] (D-NV-3)</t>
+        </is>
+      </c>
+      <c r="E614" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F614" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G614" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H614" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I614" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Oversight and Government Reform. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 398</t>
+        </is>
+      </c>
+      <c r="B615" s="48" t="inlineStr">
+        <is>
+          <t>Geothermal Cost-Recovery Authority Act of 2025</t>
+        </is>
+      </c>
+      <c r="C615" s="48" t="inlineStr"/>
+      <c r="D615" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Ocasio-Cortez, Alexandria [D-NY-14] (D-NY-14)</t>
+        </is>
+      </c>
+      <c r="E615" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F615" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G615" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H615" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I615" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 569. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5631</t>
+        </is>
+      </c>
+      <c r="B616" s="48" t="inlineStr">
+        <is>
+          <t>Geothermal Ombudsman for National Deployment and Optimal Reviews Act</t>
+        </is>
+      </c>
+      <c r="C616" s="48" t="inlineStr"/>
+      <c r="D616" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Hurd, Jeff [R-CO-3] (R-CO-3)</t>
+        </is>
+      </c>
+      <c r="E616" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F616" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G616" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H616" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I616" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 574. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5638</t>
+        </is>
+      </c>
+      <c r="B617" s="48" t="inlineStr">
+        <is>
+          <t>Geothermal Royalty Reform Act</t>
+        </is>
+      </c>
+      <c r="C617" s="48" t="inlineStr"/>
+      <c r="D617" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Kennedy, Mike [R-UT-3] (R-UT-3)</t>
+        </is>
+      </c>
+      <c r="E617" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F617" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G617" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H617" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I617" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 575. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 5617</t>
+        </is>
+      </c>
+      <c r="B618" s="48" t="inlineStr">
+        <is>
+          <t>Geothermal Gold Book Development Act</t>
+        </is>
+      </c>
+      <c r="C618" s="48" t="inlineStr"/>
+      <c r="D618" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Ansari, Yassamin [D-AZ-3] (D-AZ-3)</t>
+        </is>
+      </c>
+      <c r="E618" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F618" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G618" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H618" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 573. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8850</t>
+        </is>
+      </c>
+      <c r="B619" s="48" t="inlineStr">
+        <is>
+          <t>To create dedicated funds to conserve butterflies in North America, plants in the Pacific Islands, freshwater mussels in the United States, and desert fish in the Southwest United States, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C619" s="48" t="inlineStr"/>
+      <c r="D619" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Grijalva, Adelita S. [D-AZ-7] (D-AZ-7)</t>
+        </is>
+      </c>
+      <c r="E619" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F619" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="G619" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H619" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I619" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7450</t>
+        </is>
+      </c>
+      <c r="B620" s="48" t="inlineStr">
+        <is>
+          <t>Disaster Zone Energy Affordability and Investment Act</t>
+        </is>
+      </c>
+      <c r="C620" s="48" t="inlineStr"/>
+      <c r="D620" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Steube, W. Gregory [R-FL-17] (R-FL-17)</t>
+        </is>
+      </c>
+      <c r="E620" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F620" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G620" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="H620" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Ways and Means. 2026-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 7069</t>
+        </is>
+      </c>
+      <c r="B621" s="48" t="inlineStr">
+        <is>
+          <t>Affordable Food and Energy Act of 2026</t>
+        </is>
+      </c>
+      <c r="C621" s="48" t="inlineStr"/>
+      <c r="D621" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. McDonald Rivet, Kristen [D-MI-8] (D-MI-8)</t>
+        </is>
+      </c>
+      <c r="E621" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F621" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G621" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H621" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I621" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Subcommittee on Nutrition and Foreign Agriculture. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1318</t>
+        </is>
+      </c>
+      <c r="B622" s="48" t="inlineStr">
+        <is>
+          <t>Expressing support for the designation of the month of May 2026 as "Progressive Supranuclear Palsy and Corticobasal Degeneration Awareness Month".</t>
+        </is>
+      </c>
+      <c r="C622" s="48" t="inlineStr"/>
+      <c r="D622" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Subramanyam, Suhas [D-VA-10] (D-VA-10)</t>
+        </is>
+      </c>
+      <c r="E622" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F622" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="G622" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H622" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I622" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1315</t>
+        </is>
+      </c>
+      <c r="B623" s="48" t="inlineStr">
+        <is>
+          <t>Expressing support for the designation of May 2026 as "Renewable Fuels Month" to recognize the important role that renewable fuels play in lowering fuel prices for consumers, lessening reliance on foreign adversaries, supporting rural communities, and reducing carbon impacts.</t>
+        </is>
+      </c>
+      <c r="C623" s="48" t="inlineStr"/>
+      <c r="D623" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Nunn, Zachary [R-IA-3] (R-IA-3)</t>
+        </is>
+      </c>
+      <c r="E623" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F623" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G623" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H623" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I623" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8998</t>
+        </is>
+      </c>
+      <c r="B624" s="48" t="inlineStr">
+        <is>
+          <t>To require the Transportation Research Board to evaluate innovative hull designs and the use of alternative material construction technologies to enhance operational fleet performance and payload capacity of waterborne transit systems.</t>
+        </is>
+      </c>
+      <c r="C624" s="48" t="inlineStr"/>
+      <c r="D624" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Scholten, Hillary J. [D-MI-3] (D-MI-3)</t>
+        </is>
+      </c>
+      <c r="E624" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F624" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G624" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H624" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I624" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Transportation and Infrastructure. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8990</t>
+        </is>
+      </c>
+      <c r="B625" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Clean Air Act to exclude marginal wells from certain standards of performance and other requirements under such Act, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C625" s="48" t="inlineStr"/>
+      <c r="D625" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Pfluger, August [R-TX-11] (R-TX-11)</t>
+        </is>
+      </c>
+      <c r="E625" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="F625" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G625" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="H625" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I625" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8969</t>
+        </is>
+      </c>
+      <c r="B626" s="48" t="inlineStr">
+        <is>
+          <t>To realign the nuclear forensics and attribution activities of the Federal Government from the Department of Homeland Security to the National Nuclear Security Administration.</t>
+        </is>
+      </c>
+      <c r="C626" s="48" t="inlineStr"/>
+      <c r="D626" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Foster, Bill [D-IL-11] (D-IL-11)</t>
+        </is>
+      </c>
+      <c r="E626" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F626" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G626" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H626" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I626" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Energy and Commerce, and in addition to the Committees on Homeland Security, Armed Services, and Foreign Affairs, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 9019</t>
+        </is>
+      </c>
+      <c r="B627" s="48" t="inlineStr">
+        <is>
+          <t>To direct the Secretary of Energy to report to Congress on the use of electric energy and water by certain data centers, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C627" s="48" t="inlineStr"/>
+      <c r="D627" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Roy, Chip [R-TX-21] (R-TX-21)</t>
+        </is>
+      </c>
+      <c r="E627" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F627" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G627" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H627" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I627" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 9022</t>
+        </is>
+      </c>
+      <c r="B628" s="48" t="inlineStr">
+        <is>
+          <t>Energy and Water Development and Related Agencies Appropriations Act, 2027</t>
+        </is>
+      </c>
+      <c r="C628" s="48" t="inlineStr"/>
+      <c r="D628" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Fleischmann, Charles J. "Chuck" [R-TN-3] (R-TN-3)</t>
+        </is>
+      </c>
+      <c r="E628" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F628" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G628" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H628" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I628" s="48" t="inlineStr">
         <is>
           <t>Placed on the Union Calendar, Calendar No. 581. 2026-05-22</t>
         </is>
@@ -21866,7 +23511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I284"/>
+  <dimension ref="A1:I304"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="24" min="1" max="1"/>
@@ -32204,6 +33849,706 @@
         <v>0</v>
       </c>
       <c r="I284" s="48" t="inlineStr">
+        <is>
+          <t>Submitted in the Senate, considered, and agreed to without amendment and with a preamble by Voice Vote. (consideration: CR S2435; text: CR S2445) 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="48" t="inlineStr">
+        <is>
+          <t>S. 4351</t>
+        </is>
+      </c>
+      <c r="B285" s="48" t="inlineStr">
+        <is>
+          <t>Energy Consumer Protection Act of 2026</t>
+        </is>
+      </c>
+      <c r="C285" s="48" t="inlineStr"/>
+      <c r="D285" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Cortez Masto, Catherine [D-NV] (D-NV)</t>
+        </is>
+      </c>
+      <c r="E285" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F285" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G285" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="48" t="inlineStr">
+        <is>
+          <t>S. 1020</t>
+        </is>
+      </c>
+      <c r="B286" s="48" t="inlineStr">
+        <is>
+          <t>A bill to require the Federal Energy Regulatory Commission to extend the time period during which licensees are required to commence construction of certain hydropower projects.</t>
+        </is>
+      </c>
+      <c r="C286" s="48" t="inlineStr"/>
+      <c r="D286" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Daines, Steve [R-MT] (R-MT)</t>
+        </is>
+      </c>
+      <c r="E286" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="F286" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G286" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H286" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" s="48" t="inlineStr">
+        <is>
+          <t>Became Public Law No: 119-90. 2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="48" t="inlineStr">
+        <is>
+          <t>S. 4475</t>
+        </is>
+      </c>
+      <c r="B287" s="48" t="inlineStr">
+        <is>
+          <t>Unlock American Energy and Jobs Act of 2026</t>
+        </is>
+      </c>
+      <c r="C287" s="48" t="inlineStr"/>
+      <c r="D287" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. McCormick, David [R-PA] (R-PA)</t>
+        </is>
+      </c>
+      <c r="E287" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I287" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="48" t="inlineStr">
+        <is>
+          <t>S. 4506</t>
+        </is>
+      </c>
+      <c r="B288" s="48" t="inlineStr">
+        <is>
+          <t>Advancing Water Reuse Act</t>
+        </is>
+      </c>
+      <c r="C288" s="48" t="inlineStr"/>
+      <c r="D288" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Luján, Ben Ray [D-NM] (D-NM)</t>
+        </is>
+      </c>
+      <c r="E288" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F288" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Finance. 2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="48" t="inlineStr">
+        <is>
+          <t>S. 4559</t>
+        </is>
+      </c>
+      <c r="B289" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Federal Power Act to require the Federal Energy Regulatory Commission to issue a final rule relating to the interconnection of large load facilities with the transmission system, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C289" s="48" t="inlineStr"/>
+      <c r="D289" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Schiff, Adam B. [D-CA] (D-CA)</t>
+        </is>
+      </c>
+      <c r="E289" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="48" t="inlineStr">
+        <is>
+          <t>S. 857</t>
+        </is>
+      </c>
+      <c r="B290" s="48" t="inlineStr">
+        <is>
+          <t>Water Conservation Rebate Tax Parity Act</t>
+        </is>
+      </c>
+      <c r="C290" s="48" t="inlineStr"/>
+      <c r="D290" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Curtis, John R. [R-UT] (R-UT)</t>
+        </is>
+      </c>
+      <c r="E290" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F290" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="G290" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Finance. 2025-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="48" t="inlineStr">
+        <is>
+          <t>S. 4536</t>
+        </is>
+      </c>
+      <c r="B291" s="48" t="inlineStr">
+        <is>
+          <t>Protecting America's Drinking Water from Extreme Temperatures Act of 2026</t>
+        </is>
+      </c>
+      <c r="C291" s="48" t="inlineStr"/>
+      <c r="D291" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Rosen, Jacky [D-NV] (D-NV)</t>
+        </is>
+      </c>
+      <c r="E291" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F291" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G291" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="48" t="inlineStr">
+        <is>
+          <t>S. 4571</t>
+        </is>
+      </c>
+      <c r="B292" s="48" t="inlineStr">
+        <is>
+          <t>A bill to require the Environmental Protection Agency to establish a tropospheric ozone research program, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C292" s="48" t="inlineStr"/>
+      <c r="D292" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Whitehouse, Sheldon [D-RI] (D-RI)</t>
+        </is>
+      </c>
+      <c r="E292" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F292" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G292" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="48" t="inlineStr">
+        <is>
+          <t>S.J.RES. 188</t>
+        </is>
+      </c>
+      <c r="B293" s="48" t="inlineStr">
+        <is>
+          <t>A joint resolution providing for congressional disapproval under chapter 8 of title 5, United States Code, of the rule submitted by the Environmental Protection Agency relating to "National Emission Standards for Hazardous Air Pollutants: Coal- and Oil-Fired Electric Utility Steam Generating Units: Final Repeal".</t>
+        </is>
+      </c>
+      <c r="C293" s="48" t="inlineStr"/>
+      <c r="D293" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Whitehouse, Sheldon [D-RI] (D-RI)</t>
+        </is>
+      </c>
+      <c r="E293" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" s="48" t="inlineStr">
+        <is>
+          <t>Placed on Senate Legislative Calendar under General Orders. Calendar No. 409. 2026-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="48" t="inlineStr">
+        <is>
+          <t>S. 4406</t>
+        </is>
+      </c>
+      <c r="B294" s="48" t="inlineStr">
+        <is>
+          <t>Next-Generation Geothermal Research and Development Act</t>
+        </is>
+      </c>
+      <c r="C294" s="48" t="inlineStr"/>
+      <c r="D294" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Cortez Masto, Catherine [D-NV] (D-NV)</t>
+        </is>
+      </c>
+      <c r="E294" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F294" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H294" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="48" t="inlineStr">
+        <is>
+          <t>S. 4585</t>
+        </is>
+      </c>
+      <c r="B295" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Federal Reserve Act to mandate discount window testing, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C295" s="48" t="inlineStr"/>
+      <c r="D295" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Warner, Mark R. [D-VA] (D-VA)</t>
+        </is>
+      </c>
+      <c r="E295" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F295" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H295" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Banking, Housing, and Urban Affairs. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="48" t="inlineStr">
+        <is>
+          <t>S. 4595</t>
+        </is>
+      </c>
+      <c r="B296" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Wild and Scenic Rivers Act to designate the Mullica River watershed in New Jersey for study for potential designation as a wild and scenic river, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C296" s="48" t="inlineStr"/>
+      <c r="D296" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Kim, Andy [D-NJ] (D-NJ)</t>
+        </is>
+      </c>
+      <c r="E296" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F296" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G296" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H296" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="48" t="inlineStr">
+        <is>
+          <t>S. 4610</t>
+        </is>
+      </c>
+      <c r="B297" s="48" t="inlineStr">
+        <is>
+          <t>A bill to promote the development and use of geothermal resources in the Pacific, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C297" s="48" t="inlineStr"/>
+      <c r="D297" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Schatz, Brian [D-HI] (D-HI)</t>
+        </is>
+      </c>
+      <c r="E297" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F297" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G297" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H297" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Foreign Relations. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="48" t="inlineStr">
+        <is>
+          <t>S. 4605</t>
+        </is>
+      </c>
+      <c r="B298" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Geothermal Steam Act of 1970 to provide cost-recovery authority for the Department of the Interior.</t>
+        </is>
+      </c>
+      <c r="C298" s="48" t="inlineStr"/>
+      <c r="D298" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Gallego, Ruben [D-AZ] (D-AZ)</t>
+        </is>
+      </c>
+      <c r="E298" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="48" t="inlineStr">
+        <is>
+          <t>S. 4529</t>
+        </is>
+      </c>
+      <c r="B299" s="48" t="inlineStr">
+        <is>
+          <t>Build Nuclear with Local Materials Act of 2026</t>
+        </is>
+      </c>
+      <c r="C299" s="48" t="inlineStr"/>
+      <c r="D299" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Lummis, Cynthia M. [R-WY] (R-WY)</t>
+        </is>
+      </c>
+      <c r="E299" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F299" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" s="48" t="inlineStr">
+        <is>
+          <t>Committee on Environment and Public Works Subcommittee on Clean Air, Climate, and Nuclear Innovation and Safety. Hearings held. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="48" t="inlineStr">
+        <is>
+          <t>S. 510</t>
+        </is>
+      </c>
+      <c r="B300" s="48" t="inlineStr">
+        <is>
+          <t>Financing Our Energy Future Act</t>
+        </is>
+      </c>
+      <c r="C300" s="48" t="inlineStr"/>
+      <c r="D300" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Moran, Jerry [R-KS] (R-KS)</t>
+        </is>
+      </c>
+      <c r="E300" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F300" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G300" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="H300" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Finance. 2025-02-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="48" t="inlineStr">
+        <is>
+          <t>S. 4549</t>
+        </is>
+      </c>
+      <c r="B301" s="48" t="inlineStr">
+        <is>
+          <t>WATER for Farmers Act</t>
+        </is>
+      </c>
+      <c r="C301" s="48" t="inlineStr"/>
+      <c r="D301" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Cornyn, John [R-TX] (R-TX)</t>
+        </is>
+      </c>
+      <c r="E301" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H301" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Foreign Relations. 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="48" t="inlineStr">
+        <is>
+          <t>S. 4619</t>
+        </is>
+      </c>
+      <c r="B302" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Clean Air Act to exclude marginal wells from certain standards of performance and other requirements under that Act, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C302" s="48" t="inlineStr"/>
+      <c r="D302" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Lummis, Cynthia M. [R-WY] (R-WY)</t>
+        </is>
+      </c>
+      <c r="E302" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F302" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H302" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="48" t="inlineStr">
+        <is>
+          <t>S.RES. 752</t>
+        </is>
+      </c>
+      <c r="B303" s="48" t="inlineStr">
+        <is>
+          <t>A resolution expressing support for the designation of the month of May 2026 as "Progressive Supranuclear Palsy and Corticobasal Degeneration Awareness Month".</t>
+        </is>
+      </c>
+      <c r="C303" s="48" t="inlineStr"/>
+      <c r="D303" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Blumenthal, Richard [D-CT] (D-CT)</t>
+        </is>
+      </c>
+      <c r="E303" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Health, Education, Labor, and Pensions. (text: CR S2447) 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="48" t="inlineStr">
+        <is>
+          <t>S.RES. 747</t>
+        </is>
+      </c>
+      <c r="B304" s="48" t="inlineStr">
+        <is>
+          <t>A resolution expressing support for the designation of May 2026 as "Renewable Fuels Month" to recognize the important role that renewable fuels play in lowering fuel prices for consumers, lessening reliance on foreign adversaries, supporting rural communities, and reducing carbon impacts.</t>
+        </is>
+      </c>
+      <c r="C304" s="48" t="inlineStr"/>
+      <c r="D304" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Ricketts, Pete [R-NE] (R-NE)</t>
+        </is>
+      </c>
+      <c r="E304" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F304" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G304" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H304" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" s="48" t="inlineStr">
         <is>
           <t>Submitted in the Senate, considered, and agreed to without amendment and with a preamble by Voice Vote. (consideration: CR S2435; text: CR S2445) 2026-05-21</t>
         </is>

--- a/5.26.26 Climate Tracker .xlsx
+++ b/5.26.26 Climate Tracker .xlsx
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I628"/>
+  <dimension ref="A1:I641"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -23047,6 +23047,513 @@
         <v>0</v>
       </c>
       <c r="I628" s="48" t="inlineStr">
+        <is>
+          <t>Placed on the Union Calendar, Calendar No. 581. 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1302</t>
+        </is>
+      </c>
+      <c r="B629" s="48" t="inlineStr">
+        <is>
+          <t>Designating May 2026 as "National Electrical Safety Month" in the United States and supporting the goals and ideals of "National Electrical Safety Month" to raise awareness of electrical hazards in homes, schools, and workplaces and the action citizens can take to protect against electrically related hazards.</t>
+        </is>
+      </c>
+      <c r="C629" s="48" t="inlineStr">
+        <is>
+          <t>Tuesday, May 19. 2026</t>
+        </is>
+      </c>
+      <c r="D629" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Bresnahan, Robert P. [R-PA-8] (R-PA-8)</t>
+        </is>
+      </c>
+      <c r="E629" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F629" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G629" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H629" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I629" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8889</t>
+        </is>
+      </c>
+      <c r="B630" s="48" t="inlineStr">
+        <is>
+          <t>To improve dam and hydropower safety, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C630" s="48" t="inlineStr">
+        <is>
+          <t>Tuesday, May 19. 2026</t>
+        </is>
+      </c>
+      <c r="D630" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Dingell, Debbie [D-MI-6] (D-MI-6)</t>
+        </is>
+      </c>
+      <c r="E630" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F630" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G630" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H630" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I630" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8947</t>
+        </is>
+      </c>
+      <c r="B631" s="48" t="inlineStr">
+        <is>
+          <t>To require the Federal Energy Regulatory Commission to establish and maintain the National Utility Rate Change Tracker, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C631" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, May 20. 2026</t>
+        </is>
+      </c>
+      <c r="D631" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Vindman, Eugene Simon [D-VA-7] (D-VA-7)</t>
+        </is>
+      </c>
+      <c r="E631" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F631" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G631" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H631" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I631" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8948</t>
+        </is>
+      </c>
+      <c r="B632" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Public Utility Regulatory Policies Act of 1978 to require States to consider measures that limit the amount of retail utility rate increases an electric utility can request to once every 365 days.</t>
+        </is>
+      </c>
+      <c r="C632" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, May 20. 2026</t>
+        </is>
+      </c>
+      <c r="D632" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Vindman, Eugene Simon [D-VA-7] (D-VA-7)</t>
+        </is>
+      </c>
+      <c r="E632" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F632" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G632" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H632" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I632" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8924</t>
+        </is>
+      </c>
+      <c r="B633" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Wild and Scenic Rivers Act to designate the Mullica River watershed in New Jersey for study for potential designation as a wild and scenic river, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C633" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, May 20. 2026</t>
+        </is>
+      </c>
+      <c r="D633" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Conaway, Herbert C. [D-NJ-3] (D-NJ-3)</t>
+        </is>
+      </c>
+      <c r="E633" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F633" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G633" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H633" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I633" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8935</t>
+        </is>
+      </c>
+      <c r="B634" s="48" t="inlineStr">
+        <is>
+          <t>Department of Energy Drone Defense Act</t>
+        </is>
+      </c>
+      <c r="C634" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, May 20. 2026</t>
+        </is>
+      </c>
+      <c r="D634" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Lee, Susie [D-NV-3] (D-NV-3)</t>
+        </is>
+      </c>
+      <c r="E634" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F634" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G634" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H634" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I634" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Oversight and Government Reform. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1318</t>
+        </is>
+      </c>
+      <c r="B635" s="48" t="inlineStr">
+        <is>
+          <t>Expressing support for the designation of the month of May 2026 as "Progressive Supranuclear Palsy and Corticobasal Degeneration Awareness Month".</t>
+        </is>
+      </c>
+      <c r="C635" s="48" t="inlineStr">
+        <is>
+          <t>Thursday, May 21. 2026</t>
+        </is>
+      </c>
+      <c r="D635" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Subramanyam, Suhas [D-VA-10] (D-VA-10)</t>
+        </is>
+      </c>
+      <c r="E635" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F635" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="G635" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H635" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I635" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="48" t="inlineStr">
+        <is>
+          <t>H.RES. 1315</t>
+        </is>
+      </c>
+      <c r="B636" s="48" t="inlineStr">
+        <is>
+          <t>Expressing support for the designation of May 2026 as "Renewable Fuels Month" to recognize the important role that renewable fuels play in lowering fuel prices for consumers, lessening reliance on foreign adversaries, supporting rural communities, and reducing carbon impacts.</t>
+        </is>
+      </c>
+      <c r="C636" s="48" t="inlineStr">
+        <is>
+          <t>Thursday, May 21. 2026</t>
+        </is>
+      </c>
+      <c r="D636" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Nunn, Zachary [R-IA-3] (R-IA-3)</t>
+        </is>
+      </c>
+      <c r="E636" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F636" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G636" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H636" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I636" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8998</t>
+        </is>
+      </c>
+      <c r="B637" s="48" t="inlineStr">
+        <is>
+          <t>To require the Transportation Research Board to evaluate innovative hull designs and the use of alternative material construction technologies to enhance operational fleet performance and payload capacity of waterborne transit systems.</t>
+        </is>
+      </c>
+      <c r="C637" s="48" t="inlineStr">
+        <is>
+          <t>Thursday, May 21. 2026</t>
+        </is>
+      </c>
+      <c r="D637" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Scholten, Hillary J. [D-MI-3] (D-MI-3)</t>
+        </is>
+      </c>
+      <c r="E637" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F637" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G637" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H637" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I637" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Transportation and Infrastructure. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8990</t>
+        </is>
+      </c>
+      <c r="B638" s="48" t="inlineStr">
+        <is>
+          <t>To amend the Clean Air Act to exclude marginal wells from certain standards of performance and other requirements under such Act, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C638" s="48" t="inlineStr">
+        <is>
+          <t>Thursday, May 21. 2026</t>
+        </is>
+      </c>
+      <c r="D638" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Pfluger, August [R-TX-11] (R-TX-11)</t>
+        </is>
+      </c>
+      <c r="E638" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="F638" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G638" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="H638" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I638" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 8969</t>
+        </is>
+      </c>
+      <c r="B639" s="48" t="inlineStr">
+        <is>
+          <t>To realign the nuclear forensics and attribution activities of the Federal Government from the Department of Homeland Security to the National Nuclear Security Administration.</t>
+        </is>
+      </c>
+      <c r="C639" s="48" t="inlineStr">
+        <is>
+          <t>Thursday, May 21. 2026</t>
+        </is>
+      </c>
+      <c r="D639" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Foster, Bill [D-IL-11] (D-IL-11)</t>
+        </is>
+      </c>
+      <c r="E639" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F639" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G639" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H639" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I639" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Energy and Commerce, and in addition to the Committees on Homeland Security, Armed Services, and Foreign Affairs, for a period to be subsequently determined by the Speaker, in each case for consideration of such provisions as fall within the jurisdiction of the committee concerned. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 9019</t>
+        </is>
+      </c>
+      <c r="B640" s="48" t="inlineStr">
+        <is>
+          <t>To direct the Secretary of Energy to report to Congress on the use of electric energy and water by certain data centers, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C640" s="48" t="inlineStr">
+        <is>
+          <t>Friday, May 22. 2026</t>
+        </is>
+      </c>
+      <c r="D640" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Roy, Chip [R-TX-21] (R-TX-21)</t>
+        </is>
+      </c>
+      <c r="E640" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F640" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G640" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H640" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I640" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the House Committee on Energy and Commerce. 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="48" t="inlineStr">
+        <is>
+          <t>H.R. 9022</t>
+        </is>
+      </c>
+      <c r="B641" s="48" t="inlineStr">
+        <is>
+          <t>Energy and Water Development and Related Agencies Appropriations Act, 2027</t>
+        </is>
+      </c>
+      <c r="C641" s="48" t="inlineStr">
+        <is>
+          <t>Friday, May 22. 2026</t>
+        </is>
+      </c>
+      <c r="D641" s="48" t="inlineStr">
+        <is>
+          <t>Rep. Rep. Fleischmann, Charles J. "Chuck" [R-TN-3] (R-TN-3)</t>
+        </is>
+      </c>
+      <c r="E641" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F641" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G641" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H641" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I641" s="48" t="inlineStr">
         <is>
           <t>Placed on the Union Calendar, Calendar No. 581. 2026-05-22</t>
         </is>
@@ -23511,7 +24018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I304"/>
+  <dimension ref="A1:I313"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="24" min="1" max="1"/>
@@ -34549,6 +35056,357 @@
         <v>0</v>
       </c>
       <c r="I304" s="48" t="inlineStr">
+        <is>
+          <t>Submitted in the Senate, considered, and agreed to without amendment and with a preamble by Voice Vote. (consideration: CR S2435; text: CR S2445) 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="48" t="inlineStr">
+        <is>
+          <t>S. 4559</t>
+        </is>
+      </c>
+      <c r="B305" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Federal Power Act to require the Federal Energy Regulatory Commission to issue a final rule relating to the interconnection of large load facilities with the transmission system, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C305" s="48" t="inlineStr">
+        <is>
+          <t>Monday, May 18. 2026</t>
+        </is>
+      </c>
+      <c r="D305" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Schiff, Adam B. [D-CA] (D-CA)</t>
+        </is>
+      </c>
+      <c r="E305" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="48" t="inlineStr">
+        <is>
+          <t>S. 4571</t>
+        </is>
+      </c>
+      <c r="B306" s="48" t="inlineStr">
+        <is>
+          <t>A bill to require the Environmental Protection Agency to establish a tropospheric ozone research program, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C306" s="48" t="inlineStr">
+        <is>
+          <t>Tuesday, May 19. 2026</t>
+        </is>
+      </c>
+      <c r="D306" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Whitehouse, Sheldon [D-RI] (D-RI)</t>
+        </is>
+      </c>
+      <c r="E306" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F306" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G306" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H306" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="48" t="inlineStr">
+        <is>
+          <t>S. 4585</t>
+        </is>
+      </c>
+      <c r="B307" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Federal Reserve Act to mandate discount window testing, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C307" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, May 20. 2026</t>
+        </is>
+      </c>
+      <c r="D307" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Warner, Mark R. [D-VA] (D-VA)</t>
+        </is>
+      </c>
+      <c r="E307" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F307" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Banking, Housing, and Urban Affairs. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="48" t="inlineStr">
+        <is>
+          <t>S. 4595</t>
+        </is>
+      </c>
+      <c r="B308" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Wild and Scenic Rivers Act to designate the Mullica River watershed in New Jersey for study for potential designation as a wild and scenic river, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C308" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, May 20. 2026</t>
+        </is>
+      </c>
+      <c r="D308" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Kim, Andy [D-NJ] (D-NJ)</t>
+        </is>
+      </c>
+      <c r="E308" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G308" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="48" t="inlineStr">
+        <is>
+          <t>S. 4610</t>
+        </is>
+      </c>
+      <c r="B309" s="48" t="inlineStr">
+        <is>
+          <t>A bill to promote the development and use of geothermal resources in the Pacific, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C309" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, May 20. 2026</t>
+        </is>
+      </c>
+      <c r="D309" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Schatz, Brian [D-HI] (D-HI)</t>
+        </is>
+      </c>
+      <c r="E309" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F309" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G309" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H309" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Foreign Relations. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="48" t="inlineStr">
+        <is>
+          <t>S. 4605</t>
+        </is>
+      </c>
+      <c r="B310" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Geothermal Steam Act of 1970 to provide cost-recovery authority for the Department of the Interior.</t>
+        </is>
+      </c>
+      <c r="C310" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, May 20. 2026</t>
+        </is>
+      </c>
+      <c r="D310" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Gallego, Ruben [D-AZ] (D-AZ)</t>
+        </is>
+      </c>
+      <c r="E310" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Energy and Natural Resources. 2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="48" t="inlineStr">
+        <is>
+          <t>S. 4619</t>
+        </is>
+      </c>
+      <c r="B311" s="48" t="inlineStr">
+        <is>
+          <t>A bill to amend the Clean Air Act to exclude marginal wells from certain standards of performance and other requirements under that Act, and for other purposes.</t>
+        </is>
+      </c>
+      <c r="C311" s="48" t="inlineStr">
+        <is>
+          <t>Thursday, May 21. 2026</t>
+        </is>
+      </c>
+      <c r="D311" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Lummis, Cynthia M. [R-WY] (R-WY)</t>
+        </is>
+      </c>
+      <c r="E311" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F311" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H311" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" s="48" t="inlineStr">
+        <is>
+          <t>Read twice and referred to the Committee on Environment and Public Works. 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="48" t="inlineStr">
+        <is>
+          <t>S.RES. 752</t>
+        </is>
+      </c>
+      <c r="B312" s="48" t="inlineStr">
+        <is>
+          <t>A resolution expressing support for the designation of the month of May 2026 as "Progressive Supranuclear Palsy and Corticobasal Degeneration Awareness Month".</t>
+        </is>
+      </c>
+      <c r="C312" s="48" t="inlineStr">
+        <is>
+          <t>Thursday, May 21. 2026</t>
+        </is>
+      </c>
+      <c r="D312" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Blumenthal, Richard [D-CT] (D-CT)</t>
+        </is>
+      </c>
+      <c r="E312" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F312" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H312" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" s="48" t="inlineStr">
+        <is>
+          <t>Referred to the Committee on Health, Education, Labor, and Pensions. (text: CR S2447) 2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="48" t="inlineStr">
+        <is>
+          <t>S.RES. 747</t>
+        </is>
+      </c>
+      <c r="B313" s="48" t="inlineStr">
+        <is>
+          <t>A resolution expressing support for the designation of May 2026 as "Renewable Fuels Month" to recognize the important role that renewable fuels play in lowering fuel prices for consumers, lessening reliance on foreign adversaries, supporting rural communities, and reducing carbon impacts.</t>
+        </is>
+      </c>
+      <c r="C313" s="48" t="inlineStr">
+        <is>
+          <t>Thursday, May 21. 2026</t>
+        </is>
+      </c>
+      <c r="D313" s="48" t="inlineStr">
+        <is>
+          <t>Sen. Sen. Ricketts, Pete [R-NE] (R-NE)</t>
+        </is>
+      </c>
+      <c r="E313" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F313" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G313" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H313" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" s="48" t="inlineStr">
         <is>
           <t>Submitted in the Senate, considered, and agreed to without amendment and with a preamble by Voice Vote. (consideration: CR S2435; text: CR S2445) 2026-05-21</t>
         </is>
